--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131071609</v>
+        <v>131071465</v>
       </c>
       <c r="B2" t="n">
         <v>79243</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492127</v>
+        <v>492026</v>
       </c>
       <c r="R2" t="n">
-        <v>6720398</v>
+        <v>6720367</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131071465</v>
+        <v>131071609</v>
       </c>
       <c r="B3" t="n">
         <v>79243</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492026</v>
+        <v>492127</v>
       </c>
       <c r="R3" t="n">
-        <v>6720367</v>
+        <v>6720398</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131071465</v>
+        <v>131071609</v>
       </c>
       <c r="B2" t="n">
         <v>79243</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492026</v>
+        <v>492127</v>
       </c>
       <c r="R2" t="n">
-        <v>6720367</v>
+        <v>6720398</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131071609</v>
+        <v>131071465</v>
       </c>
       <c r="B3" t="n">
         <v>79243</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492127</v>
+        <v>492026</v>
       </c>
       <c r="R3" t="n">
-        <v>6720398</v>
+        <v>6720367</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131071609</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131071465</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131071589</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131071611</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131071690</v>
       </c>
       <c r="B6" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131071609</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131071465</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131071589</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131071611</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131071690</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131071609</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131071465</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131071589</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131071611</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131071690</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131071609</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131071465</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131071589</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131071611</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131071690</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131071609</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131071465</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131071589</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131071611</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131071690</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3061-2026 artfynd.xlsx
+++ b/artfynd/A 3061-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131071609</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131071465</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>131071589</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131071611</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131071690</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
